--- a/prova_real/trimestre_03/resultado_T3.xlsx
+++ b/prova_real/trimestre_03/resultado_T3.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R77"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>120.87</v>
+        <v>137.4</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>19.92</v>
+        <v>21.82</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-0.0433</v>
+        <v>-0.1793</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>2627.61</v>
+        <v>3053.33</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>4801.52</v>
+        <v>5275.56</v>
       </c>
     </row>
     <row r="3">
@@ -650,32 +650,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5.31</v>
+        <v>20.77</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46.45</v>
+        <v>63.61</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10.05</v>
+        <v>0.67</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>18.98</v>
+        <v>8.41</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-3.3176</v>
+        <v>0.3658</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1009.78</v>
+        <v>1413.56</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>3183.7</v>
+        <v>3635.78</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>AXIA3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -746,10 +746,10 @@
         <v>66.09999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.49</v>
+        <v>5.25</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>37.2</v>
+        <v>46.81</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6.36</v>
+        <v>10.83</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>18.57</v>
+        <v>20.11</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-4.2785</v>
+        <v>-3.5996</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>808.7</v>
+        <v>1040.22</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>2982.61</v>
+        <v>3262.44</v>
       </c>
     </row>
     <row r="5">
@@ -798,17 +798,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LAVV3</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>62.9</v>
+        <v>59.7</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16.85</v>
+        <v>7.63</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>36.01</v>
+        <v>43.37</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.64</v>
+        <v>6.44</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.2022</v>
+        <v>0.1924</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>782.83</v>
+        <v>963.78</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2956.74</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="6">
@@ -872,17 +872,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGMN3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>58.1</v>
+        <v>62.9</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7.59</v>
+        <v>16.46</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>34.44</v>
+        <v>34.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.52</v>
+        <v>6.13</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2296</v>
+        <v>0.0963</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>748.7</v>
+        <v>773.33</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2922.61</v>
+        <v>2995.56</v>
       </c>
     </row>
     <row r="7">
@@ -946,17 +946,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>62.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15.88</v>
+        <v>10.87</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>33.32</v>
+        <v>34.07</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.28</v>
+        <v>6.46</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.62</v>
+        <v>18.67</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.5732</v>
+        <v>-4.9339</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>724.35</v>
+        <v>757.11</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>2898.26</v>
+        <v>2979.33</v>
       </c>
     </row>
     <row r="8">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>62.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.41</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30.03</v>
+        <v>33.69</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.71</v>
+        <v>2.01</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>5.66</v>
+        <v>11.26</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-0.0833</v>
+        <v>-1.5214</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>652.83</v>
+        <v>748.67</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>2826.74</v>
+        <v>2970.89</v>
       </c>
     </row>
     <row r="9">
@@ -1094,32 +1094,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>22.52</v>
+        <v>15.64</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>29.9</v>
+        <v>33.05</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1145,19 +1145,19 @@
         <v>0.32</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>11.43</v>
+        <v>5.06</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-0.9262</v>
+        <v>0.4927</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>650</v>
+        <v>734.4400000000001</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>2823.91</v>
+        <v>2956.67</v>
       </c>
     </row>
     <row r="10">
@@ -1168,32 +1168,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.4</v>
+        <v>21.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>29.17</v>
+        <v>32.88</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1216,22 +1216,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>4.44</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.2845</v>
+        <v>-0.3351</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>634.13</v>
+        <v>730.67</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>2808.04</v>
+        <v>2952.89</v>
       </c>
     </row>
     <row r="11">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1264,10 +1264,10 @@
         <v>56.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14.86</v>
+        <v>14.81</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>29.04</v>
+        <v>30.33</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5.2</v>
+        <v>5.79</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.1984</v>
+        <v>0.2358</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>631.3</v>
+        <v>674</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>2805.22</v>
+        <v>2896.22</v>
       </c>
     </row>
     <row r="12">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1338,10 +1338,10 @@
         <v>61.3</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.1</v>
+        <v>4.98</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>28.39</v>
+        <v>28.69</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1364,22 +1364,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.8</v>
+        <v>0.84</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.19</v>
+        <v>6.71</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-0.4889</v>
+        <v>-0.3433</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>617.17</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>2791.09</v>
+        <v>2859.78</v>
       </c>
     </row>
     <row r="13">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>64.5</v>
+        <v>59.7</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>27</v>
+        <v>25.77</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1438,22 +1438,22 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.86</v>
+        <v>0.78</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>10.55</v>
+        <v>6.15</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-1.3445</v>
+        <v>-0.3908</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>586.96</v>
+        <v>572.67</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>2760.87</v>
+        <v>2794.89</v>
       </c>
     </row>
     <row r="14">
@@ -1464,17 +1464,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>59.7</v>
+        <v>64.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>26.08</v>
+        <v>24.56</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>5.61</v>
+        <v>5.98</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>-0.0121</v>
+        <v>0.224</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>566.96</v>
+        <v>545.78</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>2740.87</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="15">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>62.9</v>
+        <v>61.3</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.63</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1586,22 +1586,22 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.15</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.78</v>
+        <v>7.33</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5059</v>
+        <v>-0.8541</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>497.83</v>
+        <v>542.22</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>2671.74</v>
+        <v>2764.44</v>
       </c>
     </row>
     <row r="16">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1634,10 +1634,10 @@
         <v>56.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.51</v>
+        <v>4.12</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>22.62</v>
+        <v>23.46</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.13</v>
+        <v>4.75</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.1404</v>
+        <v>-0.0209</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>491.74</v>
+        <v>521.33</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>2665.65</v>
+        <v>2743.56</v>
       </c>
     </row>
     <row r="17">
@@ -1686,29 +1686,29 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4.33</v>
+        <v>10.94</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>22.32</v>
@@ -1734,22 +1734,22 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2.08</v>
+        <v>0.48</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>7.99</v>
+        <v>4.39</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-0.4954</v>
+        <v>0.4521</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>485.22</v>
+        <v>496</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>2659.13</v>
+        <v>2718.22</v>
       </c>
     </row>
     <row r="18">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>61.3</v>
+        <v>56.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5.28</v>
+        <v>16.99</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20.64</v>
+        <v>21.79</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1808,22 +1808,22 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2.19</v>
+        <v>1.24</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>5.89</v>
+        <v>4.38</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.2977</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>448.7</v>
+        <v>484.22</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>2622.61</v>
+        <v>2706.44</v>
       </c>
     </row>
     <row r="19">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>62.9</v>
+        <v>61.3</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20.38</v>
+        <v>18.91</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1882,22 +1882,22 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4.29</v>
+        <v>4.69</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-0.2342</v>
+        <v>-0.2811</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>443.04</v>
+        <v>420.22</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>2616.96</v>
+        <v>2642.44</v>
       </c>
     </row>
     <row r="20">
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>12.33</v>
+        <v>16.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>18.95</v>
+        <v>18.83</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -1956,22 +1956,22 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1.72</v>
+        <v>0.58</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.55</v>
+        <v>3.89</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.2344</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>411.96</v>
+        <v>418.44</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>2585.87</v>
+        <v>2640.67</v>
       </c>
     </row>
     <row r="21">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2004,10 +2004,10 @@
         <v>59.7</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>16.08</v>
+        <v>15.83</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>17.54</v>
+        <v>18.33</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>4.12</v>
+        <v>3.71</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.3091</v>
+        <v>0.4157</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>381.3</v>
+        <v>407.33</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>2555.22</v>
+        <v>2629.56</v>
       </c>
     </row>
     <row r="22">
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BBDC3</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>61.3</v>
+        <v>56.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.83</v>
+        <v>14.24</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>17.37</v>
+        <v>18.03</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -2104,22 +2104,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.6115</v>
+        <v>0.4056</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>377.61</v>
+        <v>400.67</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>2551.52</v>
+        <v>2622.89</v>
       </c>
     </row>
     <row r="23">
@@ -2130,17 +2130,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>17.12</v>
+        <v>17.72</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -2178,22 +2178,22 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.4009</v>
+        <v>0.6786</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>372.17</v>
+        <v>393.78</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>2546.09</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="24">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CPLE3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.46</v>
+        <v>12.28</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>16.46</v>
+        <v>17.41</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -2252,22 +2252,22 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>5.16</v>
+        <v>3.7</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.2792</v>
+        <v>0.1769</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>357.83</v>
+        <v>386.89</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>2531.74</v>
+        <v>2609.11</v>
       </c>
     </row>
     <row r="25">
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VBBR3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>56.5</v>
+        <v>64.5</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>12.49</v>
+        <v>10.92</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>16.46</v>
+        <v>17.13</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -2326,22 +2326,22 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.43</v>
+        <v>9.99</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-0.5586</v>
+        <v>-0.6402</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>357.83</v>
+        <v>380.67</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2531.74</v>
+        <v>2602.89</v>
       </c>
     </row>
     <row r="26">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VULC3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2371,13 +2371,13 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.01</v>
+        <v>15.2</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>16.33</v>
+        <v>16.05</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3.87</v>
+        <v>4.75</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.4006</v>
+        <v>0.1061</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>355</v>
+        <v>356.67</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>2528.91</v>
+        <v>2578.89</v>
       </c>
     </row>
     <row r="27">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>10.44</v>
+        <v>9.32</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>15.85</v>
+        <v>15.5</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -2474,22 +2474,22 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.2366</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>344.57</v>
+        <v>344.44</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>2518.48</v>
+        <v>2566.67</v>
       </c>
     </row>
     <row r="28">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2522,10 +2522,10 @@
         <v>59.7</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.45</v>
+        <v>5.4</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>15.02</v>
+        <v>14.35</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2548,22 +2548,22 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1.39</v>
+        <v>0.83</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>4.78</v>
+        <v>2.6</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>-0.2072</v>
+        <v>0.4129</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>326.52</v>
+        <v>318.89</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>2500.43</v>
+        <v>2541.11</v>
       </c>
     </row>
     <row r="29">
@@ -2574,32 +2574,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.65</v>
+        <v>9.18</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>14.96</v>
+        <v>13.79</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -2622,22 +2622,22 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>3.88</v>
+        <v>1.8</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.2672</v>
+        <v>0.6484</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>325.22</v>
+        <v>306.44</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>2499.13</v>
+        <v>2528.67</v>
       </c>
     </row>
     <row r="30">
@@ -2648,17 +2648,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>64.5</v>
+        <v>59.7</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.1</v>
+        <v>10.12</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>14.32</v>
+        <v>12.43</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -2696,22 +2696,22 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>10.6</v>
+        <v>2.26</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>-1.1953</v>
+        <v>0.555</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>311.3</v>
+        <v>276.22</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>2485.22</v>
+        <v>2498.44</v>
       </c>
     </row>
     <row r="31">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2744,10 +2744,10 @@
         <v>54.8</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>5.56</v>
+        <v>6.03</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>13.22</v>
+        <v>12.38</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>12.54</v>
+        <v>11.91</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>-10.9211</v>
+        <v>-12.389</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>287.39</v>
+        <v>275.11</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>2461.3</v>
+        <v>2497.33</v>
       </c>
     </row>
     <row r="32">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>MOTV3</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2815,13 +2815,13 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5.74</v>
+        <v>6.93</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>13.1</v>
+        <v>12.15</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -2844,22 +2844,22 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.58</v>
+        <v>6.52</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.5085</v>
+        <v>-1.4196</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>284.78</v>
+        <v>270</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>2458.7</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="33">
@@ -2870,17 +2870,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>NEOE3</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2892,10 +2892,10 @@
         <v>58.1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>14.34</v>
+        <v>11.21</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>12.06</v>
+        <v>11.77</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -2918,22 +2918,22 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.55</v>
+        <v>3.87</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>0.2109</v>
+        <v>0.4441</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>262.17</v>
+        <v>261.56</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>2436.09</v>
+        <v>2483.78</v>
       </c>
     </row>
     <row r="34">
@@ -2944,32 +2944,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9.49</v>
+        <v>15.42</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>11.94</v>
+        <v>11.16</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -2992,22 +2992,22 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.69</v>
+        <v>4.27</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.6397</v>
+        <v>-0.2971</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>259.57</v>
+        <v>248</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>2433.48</v>
+        <v>2470.22</v>
       </c>
     </row>
     <row r="35">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3040,10 +3040,10 @@
         <v>56.5</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>4.94</v>
+        <v>12.84</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>11.82</v>
+        <v>10.63</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1.56</v>
+        <v>0.74</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>13.21</v>
+        <v>3.37</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>-8.1213</v>
+        <v>-0.1324</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>256.96</v>
+        <v>236.22</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>2430.87</v>
+        <v>2458.44</v>
       </c>
     </row>
     <row r="36">
@@ -3092,32 +3092,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MULT3</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9.42</v>
+        <v>5.55</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>11.26</v>
+        <v>9.48</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -3140,22 +3140,22 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>-0.294</v>
+        <v>-0.4749</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>244.78</v>
+        <v>210.67</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>2418.7</v>
+        <v>2432.89</v>
       </c>
     </row>
     <row r="37">
@@ -3166,32 +3166,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>MULT3</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15.56</v>
+        <v>9.17</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.08</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -3214,22 +3214,22 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>4.05</v>
+        <v>2.53</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>-0.308</v>
+        <v>-0.1374</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>197.39</v>
+        <v>180.89</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>2371.3</v>
+        <v>2403.11</v>
       </c>
     </row>
     <row r="38">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ABCB4</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3262,10 +3262,10 @@
         <v>56.5</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.51</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>8.99</v>
+        <v>8.07</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -3288,22 +3288,22 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.67</v>
+        <v>0.29</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>-0.5472</v>
+        <v>-0.3637</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>195.43</v>
+        <v>179.33</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>2369.35</v>
+        <v>2401.56</v>
       </c>
     </row>
     <row r="39">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3333,13 +3333,13 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>8.5</v>
+        <v>6.96</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.32</v>
+        <v>1.48</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>3.14</v>
+        <v>4.78</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-2.7015</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>184.78</v>
+        <v>154.67</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>2358.7</v>
+        <v>2376.89</v>
       </c>
     </row>
     <row r="40">
@@ -3393,27 +3393,27 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>10.55</v>
+        <v>10.3</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8.32</v>
+        <v>6.28</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -3436,22 +3436,22 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>-2.2739</v>
+        <v>-1.8631</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>180.87</v>
+        <v>139.56</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>2354.78</v>
+        <v>2361.78</v>
       </c>
     </row>
     <row r="41">
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>SEER3</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>11.16</v>
+        <v>24.91</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>7.3</v>
+        <v>6.17</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -3510,22 +3510,22 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>5.05</v>
+        <v>12.26</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>-3.5042</v>
+        <v>-4.5424</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>158.7</v>
+        <v>137.11</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>2332.61</v>
+        <v>2359.33</v>
       </c>
     </row>
     <row r="42">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3558,10 +3558,10 @@
         <v>58.1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>5.68</v>
+        <v>5.19</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3587,19 +3587,19 @@
         <v>0.41</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.1185</v>
+        <v>0.1516</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>123.48</v>
+        <v>115.33</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>2297.39</v>
+        <v>2337.56</v>
       </c>
     </row>
     <row r="43">
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.38</v>
+        <v>4.1</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -3658,22 +3658,22 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3.58</v>
+        <v>0.3</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>-4.1757</v>
+        <v>-0.3022</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>109.13</v>
+        <v>111.78</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>2283.04</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="44">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3706,10 +3706,10 @@
         <v>54.8</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.02</v>
+        <v>13.23</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2.1</v>
+        <v>4.73</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.31</v>
+        <v>1.78</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.96</v>
+        <v>5.64</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>-0.4289</v>
+        <v>-5.977</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>45.65</v>
+        <v>105.11</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>2219.57</v>
+        <v>2327.33</v>
       </c>
     </row>
     <row r="45">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3780,10 +3780,10 @@
         <v>56.5</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>14.34</v>
+        <v>13.99</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.58</v>
+        <v>4.29</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -3806,22 +3806,22 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>10.74</v>
+        <v>10.46</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>-16.0576</v>
+        <v>-17.6522</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>34.35</v>
+        <v>95.33</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>2208.26</v>
+        <v>2317.56</v>
       </c>
     </row>
     <row r="46">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3854,122 +3854,122 @@
         <v>54.8</v>
       </c>
       <c r="G46" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>5.48</v>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>6.27</v>
-      </c>
       <c r="N46" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>-10.024</v>
+        <v>-7.2036</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>14.78</v>
+        <v>-44.22</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>2188.7</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>T-3</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SEER3</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>-3.6055</v>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>2173.91</v>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>2153.91</v>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>PINE4</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>-2.0624</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3980,17 +3980,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -4002,10 +4002,10 @@
         <v>53.2</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16.77</v>
+        <v>9.91</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>61.21</v>
+        <v>43.54</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>19.28</v>
+        <v>9.81</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>-1.687</v>
+        <v>0.3161</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -4076,10 +4076,10 @@
         <v>53.2</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>23.72</v>
+        <v>26.51</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>3.12</v>
+        <v>2.33</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>8.539999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>-1.3114</v>
+        <v>-0.3826</v>
       </c>
       <c r="P49" s="3" t="n">
         <v>0</v>
@@ -4128,17 +4128,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>RDOR3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -4150,10 +4150,10 @@
         <v>53.2</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>11.64</v>
+        <v>16.91</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>19.38</v>
+        <v>21.73</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>2.29</v>
+        <v>0.23</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>5.83</v>
+        <v>5.2</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>-0.3853</v>
+        <v>-0.7012</v>
       </c>
       <c r="P50" s="3" t="n">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>EQTL3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -4224,10 +4224,10 @@
         <v>53.2</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>7.75</v>
+        <v>11.78</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>13.27</v>
+        <v>19.83</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>4.7</v>
+        <v>5.81</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-0.4124</v>
+        <v>-0.3679</v>
       </c>
       <c r="P51" s="3" t="n">
         <v>0</v>
@@ -4276,17 +4276,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ANIM3</t>
+          <t>EQTL3</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -4298,10 +4298,10 @@
         <v>53.2</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>23.99</v>
+        <v>7.3</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>8.49</v>
+        <v>12.8</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>45.66</v>
+        <v>4.23</v>
       </c>
       <c r="O52" s="3" t="n">
-        <v>-56.7303</v>
+        <v>0.0361</v>
       </c>
       <c r="P52" s="3" t="n">
         <v>0</v>
@@ -4350,17 +4350,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>TFCO4</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -4372,10 +4372,10 @@
         <v>53.2</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>23.61</v>
+        <v>19.47</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>-10.38</v>
+        <v>10.96</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>11.86</v>
+        <v>5.49</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>-0.4054</v>
+        <v>-1.0378</v>
       </c>
       <c r="P53" s="3" t="n">
         <v>0</v>
@@ -4417,150 +4417,150 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>T-3</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>EZTC3</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>40.27</v>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="N54" s="4" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="O54" s="4" t="n">
-        <v>-3.2312</v>
-      </c>
-      <c r="P54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="4" t="n">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>CEAB3</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>-36.7104</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>T-3</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>TAEE11</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>26.74</v>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="N55" s="4" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="O55" s="4" t="n">
-        <v>-0.5726</v>
-      </c>
-      <c r="P55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="4" t="n">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>SMFT3</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>-1.3353</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4572,32 +4572,32 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>UGPA3</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>53.2</v>
+        <v>59.7</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>20.18</v>
+        <v>36.78</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>3.69</v>
+        <v>2.46</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>18.19</v>
+        <v>18.51</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>-17.918</v>
+        <v>-3.6893</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
@@ -4646,17 +4646,17 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>TAEE11</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>56.5</v>
+        <v>61.3</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0.89</v>
+        <v>3.39</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>17.6</v>
+        <v>27.35</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>6.66</v>
+        <v>2.97</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>11.38</v>
+        <v>7.72</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>-3.9566</v>
+        <v>-0.7155</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -4720,32 +4720,32 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1.38</v>
+        <v>3.83</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>9.49</v>
+        <v>22.62</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
@@ -4768,13 +4768,13 @@
         </is>
       </c>
       <c r="M58" s="4" t="n">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>15.05</v>
+        <v>7.47</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>-13.9775</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P58" s="4" t="n">
         <v>0</v>
@@ -4794,36 +4794,36 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>WEST3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-12.94</v>
+        <v>0.9</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>8.220000000000001</v>
+        <v>19.83</v>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="M59" s="4" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>28.89</v>
+        <v>11.88</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>-13.4336</v>
+        <v>-4.283</v>
       </c>
       <c r="P59" s="4" t="n">
         <v>0</v>
@@ -4868,32 +4868,32 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>7.08</v>
+        <v>19.05</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
@@ -4916,13 +4916,13 @@
         </is>
       </c>
       <c r="M60" s="4" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>18.64</v>
+        <v>11.72</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>-11.6042</v>
+        <v>-3.8362</v>
       </c>
       <c r="P60" s="4" t="n">
         <v>0</v>
@@ -4942,36 +4942,36 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>-4.33</v>
+        <v>2.7</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>4.16</v>
+        <v>12.16</v>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.99</v>
+        <v>3.66</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>6.56</v>
+        <v>17.99</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>-1.7523</v>
+        <v>-25.3524</v>
       </c>
       <c r="P61" s="4" t="n">
         <v>0</v>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CEED4</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>100</v>
+        <v>58.1</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0</v>
+        <v>11.57</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
@@ -5064,13 +5064,13 @@
         </is>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0</v>
+        <v>14.27</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>1</v>
+        <v>-8.869</v>
       </c>
       <c r="P62" s="4" t="n">
         <v>0</v>
@@ -5090,41 +5090,41 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-4.22</v>
+        <v>3.88</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>-6.18</v>
+        <v>10.69</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -5138,13 +5138,13 @@
         </is>
       </c>
       <c r="M63" s="4" t="n">
-        <v>0.71</v>
+        <v>1.27</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>3.59</v>
+        <v>10.77</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>-4.1645</v>
+        <v>-4.3738</v>
       </c>
       <c r="P63" s="4" t="n">
         <v>0</v>
@@ -5164,32 +5164,32 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>WEST3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.11</v>
+        <v>-11.65</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-6.47</v>
+        <v>2.69</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -5212,13 +5212,13 @@
         </is>
       </c>
       <c r="M64" s="4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>10.69</v>
+        <v>27.08</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>-9.801600000000001</v>
+        <v>-12.0452</v>
       </c>
       <c r="P64" s="4" t="n">
         <v>0</v>
@@ -5238,17 +5238,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-6.59</v>
+        <v>-4.35</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>-8.17</v>
+        <v>1.16</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -5286,13 +5286,13 @@
         </is>
       </c>
       <c r="M65" s="4" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>2.96</v>
+        <v>6.71</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>-0.0872</v>
+        <v>-1.8073</v>
       </c>
       <c r="P65" s="4" t="n">
         <v>0</v>
@@ -5312,17 +5312,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -5334,10 +5334,10 @@
         <v>54.8</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-26.45</v>
+        <v>-6.32</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>-9.529999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
@@ -5346,12 +5346,12 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -5360,13 +5360,13 @@
         </is>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.89</v>
+        <v>2.44</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>10.97</v>
+        <v>7.61</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.0405</v>
+        <v>-4.6654</v>
       </c>
       <c r="P66" s="4" t="n">
         <v>0</v>
@@ -5386,17 +5386,17 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>DXCO3</t>
+          <t>CEED4</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -5405,22 +5405,22 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>56.5</v>
+        <v>100</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-2.61</v>
+        <v>0</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>-9.890000000000001</v>
+        <v>0</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -5434,13 +5434,13 @@
         </is>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>0.0378</v>
+        <v>1</v>
       </c>
       <c r="P67" s="4" t="n">
         <v>0</v>
@@ -5460,32 +5460,32 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-12.36</v>
+        <v>-4.03</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>-12.39</v>
+        <v>-5.9</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
@@ -5508,13 +5508,13 @@
         </is>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>12.16</v>
+        <v>3.22</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>-2.1285</v>
+        <v>-2.6371</v>
       </c>
       <c r="P68" s="4" t="n">
         <v>0</v>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>VAMO3</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>59.7</v>
+        <v>53.2</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-6.95</v>
+        <v>-0.54</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>-12.85</v>
+        <v>-6.06</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="M69" s="4" t="n">
-        <v>0.38</v>
+        <v>1.4</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>12.4</v>
+        <v>10.25</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>-0.5518</v>
+        <v>-10.5621</v>
       </c>
       <c r="P69" s="4" t="n">
         <v>0</v>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>RECV3</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-5.07</v>
+        <v>-13.51</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-15.28</v>
+        <v>-6.07</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>4.73</v>
+        <v>10.16</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>-0.4178</v>
+        <v>-1.5599</v>
       </c>
       <c r="P70" s="4" t="n">
         <v>0</v>
@@ -5682,32 +5682,32 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>TUPY3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-15.31</v>
+        <v>-5.66</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>-18.43</v>
+        <v>-8.75</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="M71" s="4" t="n">
-        <v>1.56</v>
+        <v>0.97</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>11.98</v>
+        <v>1.98</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>-2.2365</v>
+        <v>0.4331</v>
       </c>
       <c r="P71" s="4" t="n">
         <v>0</v>
@@ -5756,32 +5756,32 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>RAIZ4</t>
+          <t>DXCO3</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-16.19</v>
+        <v>-2.16</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>-18.63</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>29.05</v>
+        <v>4.05</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>-2.3627</v>
+        <v>0.1234</v>
       </c>
       <c r="P72" s="4" t="n">
         <v>0</v>
@@ -5830,17 +5830,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>VAMO3</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>62.9</v>
+        <v>58.1</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>-14.78</v>
+        <v>-6.91</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>-19.57</v>
+        <v>-10.85</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
@@ -5878,13 +5878,13 @@
         </is>
       </c>
       <c r="M73" s="4" t="n">
-        <v>1.09</v>
+        <v>0.39</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>6.51</v>
+        <v>12.53</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>0.4424</v>
+        <v>-0.7211</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
@@ -5904,17 +5904,17 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>SEQL3</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -5926,10 +5926,10 @@
         <v>53.2</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-91.75</v>
+        <v>-16.14</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-23.16</v>
+        <v>-13.89</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
@@ -5952,13 +5952,13 @@
         </is>
       </c>
       <c r="M74" s="4" t="n">
-        <v>5.79</v>
+        <v>1.38</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>59.19</v>
+        <v>10.71</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>-6.4453</v>
+        <v>-1.5928</v>
       </c>
       <c r="P74" s="4" t="n">
         <v>0</v>
@@ -5978,17 +5978,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>LAND3</t>
+          <t>RECV3</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -5997,13 +5997,13 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>-29.32</v>
+        <v>-5.29</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>-24.42</v>
+        <v>-17.01</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
@@ -6026,13 +6026,13 @@
         </is>
       </c>
       <c r="M75" s="4" t="n">
-        <v>0.72</v>
+        <v>0.52</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>8.24</v>
+        <v>5.07</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>0.0529</v>
+        <v>-0.2587</v>
       </c>
       <c r="P75" s="4" t="n">
         <v>0</v>
@@ -6052,17 +6052,17 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>BRAV3</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -6071,13 +6071,13 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-3.09</v>
+        <v>-24.47</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-28.4</v>
+        <v>-17.72</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
@@ -6100,13 +6100,13 @@
         </is>
       </c>
       <c r="M76" s="4" t="n">
-        <v>1.93</v>
+        <v>0.84</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>12.69</v>
+        <v>10.57</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>-0.4515</v>
+        <v>0.0901</v>
       </c>
       <c r="P76" s="4" t="n">
         <v>0</v>
@@ -6126,69 +6126,587 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
+          <t>LAND3</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-30.09</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>-20.24</v>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>-0.2682</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>AALR3</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>-98.34999999999999</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>-23.73</v>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>-55.0747</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>SMTO3</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>-24.78</v>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>BHIA3</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>-30.46</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>-24.88</v>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>-3.1985</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>RAIZ4</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>-18.25</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>-30.77</v>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>-1.3407</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>BRAV3</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>-31.82</v>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M82" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>-1.1099</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>SEQL3</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>-91.61</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>-39.86</v>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>❌ NÃO INDICADO</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>-5.2134</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>T-3</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
           <t>GFSA3</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>Muito Previsível</t>
         </is>
       </c>
-      <c r="F77" s="4" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>-34.7</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>-60.74</v>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
+      <c r="F84" s="4" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>-38.73</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>-64.13</v>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
         <is>
           <t>❌ NÃO INDICADO</t>
         </is>
       </c>
-      <c r="M77" s="4" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>73.06999999999999</v>
-      </c>
-      <c r="O77" s="4" t="n">
-        <v>-2.8354</v>
-      </c>
-      <c r="P77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="4" t="n">
+      <c r="M84" s="4" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>-2.3186</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6203,7 +6721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6331,12 +6849,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -6345,13 +6863,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>120.87</v>
+        <v>137.4</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -6374,22 +6892,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>19.92</v>
+        <v>21.82</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-0.0433</v>
+        <v>-0.1793</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>2627.61</v>
+        <v>3053.33</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>4801.52</v>
+        <v>5275.56</v>
       </c>
     </row>
     <row r="3">
@@ -6400,32 +6918,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AXIA3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5.31</v>
+        <v>20.77</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46.45</v>
+        <v>63.61</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -6448,22 +6966,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>10.05</v>
+        <v>0.67</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>18.98</v>
+        <v>8.41</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-3.3176</v>
+        <v>0.3658</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>1009.78</v>
+        <v>1413.56</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>3183.7</v>
+        <v>3635.78</v>
       </c>
     </row>
     <row r="4">
@@ -6474,17 +6992,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>AXIA3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6496,10 +7014,10 @@
         <v>66.09999999999999</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.49</v>
+        <v>5.25</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>37.2</v>
+        <v>46.81</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -6522,22 +7040,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6.36</v>
+        <v>10.83</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>18.57</v>
+        <v>20.11</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-4.2785</v>
+        <v>-3.5996</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>808.7</v>
+        <v>1040.22</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>2982.61</v>
+        <v>3262.44</v>
       </c>
     </row>
     <row r="5">
@@ -6548,17 +7066,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LAVV3</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6567,13 +7085,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>62.9</v>
+        <v>59.7</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16.85</v>
+        <v>7.63</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>36.01</v>
+        <v>43.37</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -6596,22 +7114,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5.64</v>
+        <v>6.44</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.2022</v>
+        <v>0.1924</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>782.83</v>
+        <v>963.78</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2956.74</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="6">
@@ -6622,17 +7140,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGMN3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6641,13 +7159,13 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>58.1</v>
+        <v>62.9</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7.59</v>
+        <v>16.46</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>34.44</v>
+        <v>34.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -6670,22 +7188,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.52</v>
+        <v>6.13</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2296</v>
+        <v>0.0963</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>748.7</v>
+        <v>773.33</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2922.61</v>
+        <v>2995.56</v>
       </c>
     </row>
     <row r="7">
@@ -6696,17 +7214,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6715,13 +7233,13 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>62.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15.88</v>
+        <v>10.87</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>33.32</v>
+        <v>34.07</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -6744,22 +7262,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.28</v>
+        <v>6.46</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.62</v>
+        <v>18.67</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.5732</v>
+        <v>-4.9339</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>724.35</v>
+        <v>757.11</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>2898.26</v>
+        <v>2979.33</v>
       </c>
     </row>
     <row r="8">
@@ -6770,17 +7288,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6789,13 +7307,13 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>62.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5.41</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30.03</v>
+        <v>33.69</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -6818,22 +7336,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.71</v>
+        <v>2.01</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>5.66</v>
+        <v>11.26</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-0.0833</v>
+        <v>-1.5214</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>652.83</v>
+        <v>748.67</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>2826.74</v>
+        <v>2970.89</v>
       </c>
     </row>
     <row r="9">
@@ -6844,32 +7362,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>COGN3</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>22.52</v>
+        <v>15.64</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>29.9</v>
+        <v>33.05</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -6895,19 +7413,19 @@
         <v>0.32</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>11.43</v>
+        <v>5.06</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>-0.9262</v>
+        <v>0.4927</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>650</v>
+        <v>734.4400000000001</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>2823.91</v>
+        <v>2956.67</v>
       </c>
     </row>
     <row r="10">
@@ -6918,32 +7436,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>COGN3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8.4</v>
+        <v>21.65</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>29.17</v>
+        <v>32.88</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -6966,22 +7484,22 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>4.44</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.2845</v>
+        <v>-0.3351</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>634.13</v>
+        <v>730.67</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>2808.04</v>
+        <v>2952.89</v>
       </c>
     </row>
     <row r="11">
@@ -6997,12 +7515,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -7014,10 +7532,10 @@
         <v>56.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14.86</v>
+        <v>14.81</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>29.04</v>
+        <v>30.33</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -7040,22 +7558,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5.2</v>
+        <v>5.79</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.1984</v>
+        <v>0.2358</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>631.3</v>
+        <v>674</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>2805.22</v>
+        <v>2896.22</v>
       </c>
     </row>
     <row r="12">
@@ -7066,17 +7584,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7088,10 +7606,10 @@
         <v>61.3</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10.1</v>
+        <v>4.98</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>28.39</v>
+        <v>28.69</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -7114,22 +7632,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.8</v>
+        <v>0.84</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6.19</v>
+        <v>6.71</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>-0.4889</v>
+        <v>-0.3433</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>617.17</v>
+        <v>637.5599999999999</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>2791.09</v>
+        <v>2859.78</v>
       </c>
     </row>
     <row r="13">
@@ -7140,17 +7658,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7159,13 +7677,13 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>64.5</v>
+        <v>59.7</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8.109999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>27</v>
+        <v>25.77</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -7188,22 +7706,22 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1.86</v>
+        <v>0.78</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>10.55</v>
+        <v>6.15</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>-1.3445</v>
+        <v>-0.3908</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>586.96</v>
+        <v>572.67</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>2760.87</v>
+        <v>2794.89</v>
       </c>
     </row>
     <row r="14">
@@ -7214,17 +7732,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7233,13 +7751,13 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>59.7</v>
+        <v>64.5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>26.08</v>
+        <v>24.56</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -7262,22 +7780,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>5.61</v>
+        <v>5.98</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>-0.0121</v>
+        <v>0.224</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>566.96</v>
+        <v>545.78</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>2740.87</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="15">
@@ -7288,17 +7806,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7307,13 +7825,13 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>62.9</v>
+        <v>61.3</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.63</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -7336,22 +7854,22 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.15</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.78</v>
+        <v>7.33</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.5059</v>
+        <v>-0.8541</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>497.83</v>
+        <v>542.22</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>2671.74</v>
+        <v>2764.44</v>
       </c>
     </row>
     <row r="16">
@@ -7367,12 +7885,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7384,10 +7902,10 @@
         <v>56.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4.51</v>
+        <v>4.12</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>22.62</v>
+        <v>23.46</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -7410,22 +7928,22 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>4.13</v>
+        <v>4.75</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.1404</v>
+        <v>-0.0209</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>491.74</v>
+        <v>521.33</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>2665.65</v>
+        <v>2743.56</v>
       </c>
     </row>
     <row r="17">
@@ -7436,29 +7954,29 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4.33</v>
+        <v>10.94</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>22.32</v>
@@ -7484,22 +8002,22 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2.08</v>
+        <v>0.48</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>7.99</v>
+        <v>4.39</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>-0.4954</v>
+        <v>0.4521</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>485.22</v>
+        <v>496</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>2659.13</v>
+        <v>2718.22</v>
       </c>
     </row>
     <row r="18">
@@ -7510,17 +8028,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -7529,13 +8047,13 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>61.3</v>
+        <v>56.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5.28</v>
+        <v>16.99</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>20.64</v>
+        <v>21.79</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -7558,22 +8076,22 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2.19</v>
+        <v>1.24</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>5.89</v>
+        <v>4.38</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.2977</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>448.7</v>
+        <v>484.22</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>2622.61</v>
+        <v>2706.44</v>
       </c>
     </row>
     <row r="19">
@@ -7589,12 +8107,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -7603,13 +8121,13 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>62.9</v>
+        <v>61.3</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>20.38</v>
+        <v>18.91</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -7632,22 +8150,22 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4.29</v>
+        <v>4.69</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>-0.2342</v>
+        <v>-0.2811</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>443.04</v>
+        <v>420.22</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>2616.96</v>
+        <v>2642.44</v>
       </c>
     </row>
     <row r="20">
@@ -7658,17 +8176,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -7677,13 +8195,13 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>12.33</v>
+        <v>16.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>18.95</v>
+        <v>18.83</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -7706,22 +8224,22 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1.72</v>
+        <v>0.58</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.55</v>
+        <v>3.89</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.2344</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>411.96</v>
+        <v>418.44</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>2585.87</v>
+        <v>2640.67</v>
       </c>
     </row>
     <row r="21">
@@ -7737,12 +8255,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -7754,10 +8272,10 @@
         <v>59.7</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>16.08</v>
+        <v>15.83</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>17.54</v>
+        <v>18.33</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -7780,22 +8298,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>4.12</v>
+        <v>3.71</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.3091</v>
+        <v>0.4157</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>381.3</v>
+        <v>407.33</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>2555.22</v>
+        <v>2629.56</v>
       </c>
     </row>
     <row r="22">
@@ -7806,17 +8324,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BBDC3</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -7825,13 +8343,13 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>61.3</v>
+        <v>56.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13.83</v>
+        <v>14.24</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>17.37</v>
+        <v>18.03</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -7854,22 +8372,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.6115</v>
+        <v>0.4056</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>377.61</v>
+        <v>400.67</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>2551.52</v>
+        <v>2622.89</v>
       </c>
     </row>
     <row r="23">
@@ -7880,17 +8398,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -7899,13 +8417,13 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>13.63</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>17.12</v>
+        <v>17.72</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -7928,22 +8446,22 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.4009</v>
+        <v>0.6786</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>372.17</v>
+        <v>393.78</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>2546.09</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="24">
@@ -7954,17 +8472,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CPLE3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -7973,13 +8491,13 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11.46</v>
+        <v>12.28</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>16.46</v>
+        <v>17.41</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -8002,22 +8520,22 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>5.16</v>
+        <v>3.7</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0.2792</v>
+        <v>0.1769</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>357.83</v>
+        <v>386.89</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>2531.74</v>
+        <v>2609.11</v>
       </c>
     </row>
     <row r="25">
@@ -8028,17 +8546,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VBBR3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8047,13 +8565,13 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>56.5</v>
+        <v>64.5</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>12.49</v>
+        <v>10.92</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>16.46</v>
+        <v>17.13</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -8076,22 +8594,22 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.43</v>
+        <v>9.99</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>-0.5586</v>
+        <v>-0.6402</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>357.83</v>
+        <v>380.67</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2531.74</v>
+        <v>2602.89</v>
       </c>
     </row>
     <row r="26">
@@ -8102,17 +8620,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VULC3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8121,13 +8639,13 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11.01</v>
+        <v>15.2</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>16.33</v>
+        <v>16.05</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -8150,22 +8668,22 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3.87</v>
+        <v>4.75</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.4006</v>
+        <v>0.1061</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>355</v>
+        <v>356.67</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>2528.91</v>
+        <v>2578.89</v>
       </c>
     </row>
     <row r="27">
@@ -8176,17 +8694,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>IGTI11</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -8195,13 +8713,13 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>10.44</v>
+        <v>9.32</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>15.85</v>
+        <v>15.5</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -8224,22 +8742,22 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.2366</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>344.57</v>
+        <v>344.44</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>2518.48</v>
+        <v>2566.67</v>
       </c>
     </row>
     <row r="28">
@@ -8250,17 +8768,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8272,10 +8790,10 @@
         <v>59.7</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15.45</v>
+        <v>5.4</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>15.02</v>
+        <v>14.35</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -8298,22 +8816,22 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1.39</v>
+        <v>0.83</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>4.78</v>
+        <v>2.6</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>-0.2072</v>
+        <v>0.4129</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>326.52</v>
+        <v>318.89</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>2500.43</v>
+        <v>2541.11</v>
       </c>
     </row>
     <row r="29">
@@ -8324,32 +8842,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.65</v>
+        <v>9.18</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>14.96</v>
+        <v>13.79</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -8372,22 +8890,22 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1.09</v>
+        <v>0.82</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>3.88</v>
+        <v>1.8</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.2672</v>
+        <v>0.6484</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>325.22</v>
+        <v>306.44</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>2499.13</v>
+        <v>2528.67</v>
       </c>
     </row>
     <row r="30">
@@ -8398,17 +8916,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>IGTI11</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8417,13 +8935,13 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>64.5</v>
+        <v>59.7</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.1</v>
+        <v>10.12</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>14.32</v>
+        <v>12.43</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -8446,22 +8964,22 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>10.6</v>
+        <v>2.26</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>-1.1953</v>
+        <v>0.555</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>311.3</v>
+        <v>276.22</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>2485.22</v>
+        <v>2498.44</v>
       </c>
     </row>
     <row r="31">
@@ -8477,12 +8995,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -8494,10 +9012,10 @@
         <v>54.8</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>5.56</v>
+        <v>6.03</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>13.22</v>
+        <v>12.38</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -8520,22 +9038,22 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>12.54</v>
+        <v>11.91</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>-10.9211</v>
+        <v>-12.389</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>287.39</v>
+        <v>275.11</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>2461.3</v>
+        <v>2497.33</v>
       </c>
     </row>
     <row r="32">
@@ -8546,17 +9064,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>MOTV3</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8565,13 +9083,13 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>59.7</v>
+        <v>56.5</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5.74</v>
+        <v>6.93</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>13.1</v>
+        <v>12.15</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -8594,22 +9112,22 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.58</v>
+        <v>6.52</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.5085</v>
+        <v>-1.4196</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>284.78</v>
+        <v>270</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>2458.7</v>
+        <v>2492.22</v>
       </c>
     </row>
     <row r="33">
@@ -8620,17 +9138,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>NEOE3</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -8642,10 +9160,10 @@
         <v>58.1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>14.34</v>
+        <v>11.21</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>12.06</v>
+        <v>11.77</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -8668,22 +9186,22 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.55</v>
+        <v>3.87</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>0.2109</v>
+        <v>0.4441</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>262.17</v>
+        <v>261.56</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>2436.09</v>
+        <v>2483.78</v>
       </c>
     </row>
     <row r="34">
@@ -8694,32 +9212,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9.49</v>
+        <v>15.42</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>11.94</v>
+        <v>11.16</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -8742,22 +9260,22 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.69</v>
+        <v>4.27</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.6397</v>
+        <v>-0.2971</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>259.57</v>
+        <v>248</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>2433.48</v>
+        <v>2470.22</v>
       </c>
     </row>
     <row r="35">
@@ -8768,17 +9286,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>VBBR3</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -8790,10 +9308,10 @@
         <v>56.5</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>4.94</v>
+        <v>12.84</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>11.82</v>
+        <v>10.63</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -8816,22 +9334,22 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1.56</v>
+        <v>0.74</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>13.21</v>
+        <v>3.37</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>-8.1213</v>
+        <v>-0.1324</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>256.96</v>
+        <v>236.22</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>2430.87</v>
+        <v>2458.44</v>
       </c>
     </row>
     <row r="36">
@@ -8842,32 +9360,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MULT3</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>9.42</v>
+        <v>5.55</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>11.26</v>
+        <v>9.48</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -8890,22 +9408,22 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.73</v>
+        <v>3.19</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>-0.294</v>
+        <v>-0.4749</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>244.78</v>
+        <v>210.67</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>2418.7</v>
+        <v>2432.89</v>
       </c>
     </row>
     <row r="37">
@@ -8916,32 +9434,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>MULT3</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15.56</v>
+        <v>9.17</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.08</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -8964,22 +9482,22 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>4.05</v>
+        <v>2.53</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>-0.308</v>
+        <v>-0.1374</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>197.39</v>
+        <v>180.89</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>2371.3</v>
+        <v>2403.11</v>
       </c>
     </row>
     <row r="38">
@@ -8990,17 +9508,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ABCB4</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9012,10 +9530,10 @@
         <v>56.5</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.51</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>8.99</v>
+        <v>8.07</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -9038,22 +9556,22 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.67</v>
+        <v>0.29</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>-0.5472</v>
+        <v>-0.3637</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>195.43</v>
+        <v>179.33</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>2369.35</v>
+        <v>2401.56</v>
       </c>
     </row>
     <row r="39">
@@ -9064,17 +9582,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -9083,13 +9601,13 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>10.86</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>8.5</v>
+        <v>6.96</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -9112,22 +9630,22 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.32</v>
+        <v>1.48</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>3.14</v>
+        <v>4.78</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-2.7015</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>184.78</v>
+        <v>154.67</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>2358.7</v>
+        <v>2376.89</v>
       </c>
     </row>
     <row r="40">
@@ -9143,27 +9661,27 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>10.55</v>
+        <v>10.3</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8.32</v>
+        <v>6.28</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -9186,22 +9704,22 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>-2.2739</v>
+        <v>-1.8631</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>180.87</v>
+        <v>139.56</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>2354.78</v>
+        <v>2361.78</v>
       </c>
     </row>
     <row r="41">
@@ -9212,17 +9730,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>SEER3</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9231,13 +9749,13 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>11.16</v>
+        <v>24.91</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>7.3</v>
+        <v>6.17</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -9260,22 +9778,22 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>5.05</v>
+        <v>12.26</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>-3.5042</v>
+        <v>-4.5424</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>158.7</v>
+        <v>137.11</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>2332.61</v>
+        <v>2359.33</v>
       </c>
     </row>
     <row r="42">
@@ -9291,12 +9809,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9308,10 +9826,10 @@
         <v>58.1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>11.83</v>
+        <v>11.97</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>5.68</v>
+        <v>5.19</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -9337,19 +9855,19 @@
         <v>0.41</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>0.1185</v>
+        <v>0.1516</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>123.48</v>
+        <v>115.33</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>2297.39</v>
+        <v>2337.56</v>
       </c>
     </row>
     <row r="43">
@@ -9360,32 +9878,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.38</v>
+        <v>4.1</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>5.02</v>
+        <v>5.03</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -9408,22 +9926,22 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3.58</v>
+        <v>0.3</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>2.82</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>-4.1757</v>
+        <v>-0.3022</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>109.13</v>
+        <v>111.78</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>2283.04</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="44">
@@ -9434,17 +9952,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9456,10 +9974,10 @@
         <v>54.8</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4.02</v>
+        <v>13.23</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2.1</v>
+        <v>4.73</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -9482,22 +10000,22 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.31</v>
+        <v>1.78</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.96</v>
+        <v>5.64</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>-0.4289</v>
+        <v>-5.977</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>45.65</v>
+        <v>105.11</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>2219.57</v>
+        <v>2327.33</v>
       </c>
     </row>
     <row r="45">
@@ -9513,12 +10031,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9530,10 +10048,10 @@
         <v>56.5</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>14.34</v>
+        <v>13.99</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.58</v>
+        <v>4.29</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -9556,22 +10074,22 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>10.74</v>
+        <v>10.46</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>-16.0576</v>
+        <v>-17.6522</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>34.35</v>
+        <v>95.33</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>2208.26</v>
+        <v>2317.56</v>
       </c>
     </row>
     <row r="46">
@@ -9587,12 +10105,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9604,122 +10122,48 @@
         <v>54.8</v>
       </c>
       <c r="G46" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
         <v>5.48</v>
       </c>
-      <c r="H46" s="2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>6.27</v>
-      </c>
       <c r="N46" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>-10.024</v>
+        <v>-7.2036</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>2173.91</v>
+        <v>2222.22</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>14.78</v>
+        <v>-44.22</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>2188.7</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>T-3</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SEER3</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>✅ COMPRAR</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>-3.6055</v>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>2173.91</v>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>2153.91</v>
+        <v>2178</v>
       </c>
     </row>
   </sheetData>
